--- a/research/traditional_assets/database/data/canada/canada_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_insurance_life.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.03365</v>
+        <v>0.0271</v>
       </c>
       <c r="E2">
-        <v>0.1555</v>
+        <v>0.0579</v>
       </c>
       <c r="G2">
-        <v>0.09460037284175657</v>
+        <v>0.1952258814019851</v>
       </c>
       <c r="H2">
-        <v>0.09460037284175657</v>
+        <v>0.1952258814019851</v>
       </c>
       <c r="I2">
-        <v>0.1104617022871237</v>
+        <v>0.145809458657956</v>
       </c>
       <c r="J2">
-        <v>0.09646238564948013</v>
+        <v>0.1287677350607608</v>
       </c>
       <c r="K2">
-        <v>14789.6</v>
+        <v>11772.7</v>
       </c>
       <c r="L2">
-        <v>0.07846016566736445</v>
+        <v>0.1029872577030273</v>
       </c>
       <c r="M2">
-        <v>5348.9</v>
+        <v>6982.2968</v>
       </c>
       <c r="N2">
-        <v>0.04158933476813648</v>
+        <v>0.06563049216077001</v>
       </c>
       <c r="O2">
-        <v>0.361666306052902</v>
+        <v>0.593092221835263</v>
       </c>
       <c r="P2">
-        <v>5166.34</v>
+        <v>5503.1968</v>
       </c>
       <c r="Q2">
-        <v>0.04016987488754964</v>
+        <v>0.05172760837688461</v>
       </c>
       <c r="R2">
-        <v>0.3493224968897063</v>
+        <v>0.4674540929438447</v>
       </c>
       <c r="S2">
-        <v>182.56</v>
+        <v>1479.1</v>
       </c>
       <c r="T2">
-        <v>0.03413038194769018</v>
+        <v>0.2118357386354588</v>
       </c>
       <c r="U2">
-        <v>38972.9</v>
+        <v>37387.4</v>
       </c>
       <c r="V2">
-        <v>0.3030262268849869</v>
+        <v>0.3514249727412866</v>
       </c>
       <c r="W2">
-        <v>0.1588575876952394</v>
+        <v>0.1158680068845084</v>
       </c>
       <c r="X2">
-        <v>0.06389531784763143</v>
+        <v>0.09916869386813962</v>
       </c>
       <c r="Y2">
-        <v>0.09496226984760796</v>
+        <v>0.01669931301636873</v>
       </c>
       <c r="Z2">
-        <v>2.029991067502732</v>
+        <v>1.157457106261043</v>
       </c>
       <c r="AA2">
-        <v>0.2335481516388917</v>
+        <v>0.1438050690044427</v>
       </c>
       <c r="AB2">
-        <v>0.05347014928586036</v>
+        <v>0.08318609123616622</v>
       </c>
       <c r="AC2">
-        <v>0.1806527477263157</v>
+        <v>0.06102680899293927</v>
       </c>
       <c r="AD2">
-        <v>45502.2</v>
+        <v>50301.4</v>
       </c>
       <c r="AE2">
-        <v>0.7647497065074053</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>45502.96474970651</v>
+        <v>50301.4</v>
       </c>
       <c r="AG2">
-        <v>6530.064749706507</v>
+        <v>12914</v>
       </c>
       <c r="AH2">
-        <v>0.2613381705223706</v>
+        <v>0.3210261830091889</v>
       </c>
       <c r="AI2">
-        <v>0.2501522726781066</v>
+        <v>0.2843646210508761</v>
       </c>
       <c r="AJ2">
-        <v>0.04831989407467201</v>
+        <v>0.1082462993076394</v>
       </c>
       <c r="AK2">
-        <v>0.04568773943989172</v>
+        <v>0.0925714195598521</v>
       </c>
       <c r="AL2">
-        <v>1842.2</v>
+        <v>1907.3</v>
       </c>
       <c r="AM2">
-        <v>1842.2</v>
+        <v>1907.3</v>
       </c>
       <c r="AN2">
-        <v>2.034273845175103</v>
+        <v>2.739280074061972</v>
       </c>
       <c r="AO2">
-        <v>11.30235587884052</v>
+        <v>8.73895034866041</v>
       </c>
       <c r="AP2">
-        <v>0.2919406078745172</v>
+        <v>0.7032619942275228</v>
       </c>
       <c r="AQ2">
-        <v>11.30235587884052</v>
+        <v>8.73895034866041</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sun Life Financial Inc. (TSX:SLF)</t>
+          <t>Power Corporation of Canada (TSX:POW)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,121 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0157</v>
+        <v>0.0271</v>
       </c>
       <c r="E3">
-        <v>0.09089999999999999</v>
+        <v>0.0579</v>
       </c>
       <c r="G3">
-        <v>0.1068513425450368</v>
+        <v>0.1215302389834279</v>
       </c>
       <c r="H3">
-        <v>0.1068513425450368</v>
+        <v>0.1215302389834279</v>
       </c>
       <c r="I3">
-        <v>0.1386652234261499</v>
+        <v>0.08380976525918758</v>
       </c>
       <c r="J3">
-        <v>0.1158732238580228</v>
+        <v>0.07504304142086674</v>
       </c>
       <c r="K3">
-        <v>2920.8</v>
+        <v>1533.2</v>
       </c>
       <c r="L3">
-        <v>0.1075361454432994</v>
+        <v>0.03966328119745236</v>
       </c>
       <c r="M3">
-        <v>1019.64</v>
+        <v>1233.8</v>
       </c>
       <c r="N3">
-        <v>0.03127250421714461</v>
+        <v>0.07852496785937042</v>
       </c>
       <c r="O3">
-        <v>0.3490961380443714</v>
+        <v>0.8047221497521523</v>
       </c>
       <c r="P3">
-        <v>1019.64</v>
+        <v>948.3</v>
       </c>
       <c r="Q3">
-        <v>0.03127250421714461</v>
+        <v>0.06035437430786268</v>
       </c>
       <c r="R3">
-        <v>0.3490961380443714</v>
+        <v>0.6185103052439342</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>285.5</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.2313989301345437</v>
       </c>
       <c r="U3">
-        <v>6587.4</v>
+        <v>8222.4</v>
       </c>
       <c r="V3">
-        <v>0.2020364974697132</v>
+        <v>0.523313094283423</v>
       </c>
       <c r="W3">
-        <v>0.1648604714169602</v>
+        <v>0.08412019993086914</v>
       </c>
       <c r="X3">
-        <v>0.05891425896337998</v>
+        <v>0.1189353155788761</v>
       </c>
       <c r="Y3">
-        <v>0.1059462124535802</v>
+        <v>-0.03481511564800695</v>
       </c>
       <c r="Z3">
-        <v>2.440525823958596</v>
+        <v>2.482477378253582</v>
       </c>
       <c r="AA3">
-        <v>0.2827915951308398</v>
+        <v>0.1862926527226482</v>
       </c>
       <c r="AB3">
-        <v>0.05416024092711963</v>
+        <v>0.0803611296377883</v>
       </c>
       <c r="AC3">
-        <v>0.2286313542037202</v>
+        <v>0.1059315230848599</v>
       </c>
       <c r="AD3">
-        <v>4368.1</v>
+        <v>14418.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4368.1</v>
+        <v>14418.2</v>
       </c>
       <c r="AG3">
-        <v>-2219.299999999999</v>
+        <v>6195.800000000001</v>
       </c>
       <c r="AH3">
-        <v>0.1181426496561013</v>
+        <v>0.4785266707378594</v>
       </c>
       <c r="AI3">
-        <v>0.1667659298285802</v>
+        <v>0.3153373240222119</v>
       </c>
       <c r="AJ3">
-        <v>-0.07303764599795295</v>
+        <v>0.2828099324447691</v>
       </c>
       <c r="AK3">
-        <v>-0.1131972497653731</v>
+        <v>0.1652182492593472</v>
       </c>
       <c r="AL3">
-        <v>264.2</v>
+        <v>423.2</v>
       </c>
       <c r="AM3">
-        <v>264.2</v>
+        <v>423.2</v>
       </c>
       <c r="AN3">
-        <v>1.081400242616295</v>
+        <v>3.875339336110738</v>
       </c>
       <c r="AO3">
-        <v>14.2554882664648</v>
+        <v>7.655245746691871</v>
       </c>
       <c r="AP3">
-        <v>-0.5494268808952044</v>
+        <v>1.665313801908346</v>
       </c>
       <c r="AQ3">
-        <v>14.2554882664648</v>
+        <v>7.655245746691871</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>E-L Financial Corporation Limited (TSX:ELF)</t>
+          <t>Sun Life Financial Inc. (TSX:SLF)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,121 +856,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0181</v>
+        <v>0.008229999999999999</v>
       </c>
       <c r="E4">
-        <v>0.26</v>
+        <v>0.0342</v>
       </c>
       <c r="G4">
-        <v>0.2918410041841004</v>
+        <v>0.2465198973262521</v>
       </c>
       <c r="H4">
-        <v>0.2918410041841004</v>
+        <v>0.2465198973262521</v>
       </c>
       <c r="I4">
-        <v>0.7295776051006178</v>
+        <v>0.1830462546377549</v>
       </c>
       <c r="J4">
-        <v>0.619662743598326</v>
+        <v>0.1515489359592129</v>
       </c>
       <c r="K4">
-        <v>1104.6</v>
+        <v>2381</v>
       </c>
       <c r="L4">
-        <v>0.5502092050209205</v>
+        <v>0.1361170343522579</v>
       </c>
       <c r="M4">
-        <v>81.3</v>
+        <v>1155.208</v>
       </c>
       <c r="N4">
-        <v>0.03161332970408679</v>
+        <v>0.04242315630210131</v>
       </c>
       <c r="O4">
-        <v>0.07360130363932646</v>
+        <v>0.485177656446871</v>
       </c>
       <c r="P4">
-        <v>15.8</v>
+        <v>1155.208</v>
       </c>
       <c r="Q4">
-        <v>0.006143795932651555</v>
+        <v>0.04242315630210131</v>
       </c>
       <c r="R4">
-        <v>0.01430382038747058</v>
+        <v>0.485177656446871</v>
       </c>
       <c r="S4">
-        <v>65.5</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.8056580565805659</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>430.8</v>
+        <v>6843.7</v>
       </c>
       <c r="V4">
-        <v>0.1675156511257145</v>
+        <v>0.2513238782839893</v>
       </c>
       <c r="W4">
-        <v>0.241553499967198</v>
+        <v>0.1203808098529241</v>
       </c>
       <c r="X4">
-        <v>0.06221868760187976</v>
+        <v>0.09592067239384906</v>
       </c>
       <c r="Y4">
-        <v>0.1793348123653183</v>
+        <v>0.02446013745907501</v>
       </c>
       <c r="Z4">
-        <v>0.4329896907216495</v>
+        <v>1.214878042004667</v>
       </c>
       <c r="AA4">
-        <v>0.268307579702368</v>
+        <v>0.1841134745860192</v>
       </c>
       <c r="AB4">
-        <v>0.05375840718465279</v>
+        <v>0.08363421015314147</v>
       </c>
       <c r="AC4">
-        <v>0.2145491725177152</v>
+        <v>0.1004792644328777</v>
       </c>
       <c r="AD4">
-        <v>634.4</v>
+        <v>7384.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>634.4</v>
+        <v>7384.1</v>
       </c>
       <c r="AG4">
-        <v>203.6</v>
+        <v>540.4000000000005</v>
       </c>
       <c r="AH4">
-        <v>0.1978728049655344</v>
+        <v>0.213322663492678</v>
       </c>
       <c r="AI4">
-        <v>0.08828768648407927</v>
+        <v>0.2604629998694881</v>
       </c>
       <c r="AJ4">
-        <v>0.07336143840305552</v>
+        <v>0.01945914803211986</v>
       </c>
       <c r="AK4">
-        <v>0.03014152898679457</v>
+        <v>0.0251276376114795</v>
       </c>
       <c r="AL4">
-        <v>23.1</v>
+        <v>291.3</v>
       </c>
       <c r="AM4">
-        <v>23.1</v>
+        <v>291.3</v>
       </c>
       <c r="AN4">
-        <v>0.4300433839479392</v>
+        <v>2.121684912220211</v>
       </c>
       <c r="AO4">
-        <v>63.4069264069264</v>
+        <v>10.99176107106076</v>
       </c>
       <c r="AP4">
-        <v>0.1380151843817787</v>
+        <v>0.1552739706347155</v>
       </c>
       <c r="AQ4">
-        <v>63.4069264069264</v>
+        <v>10.99176107106076</v>
       </c>
     </row>
     <row r="5">
@@ -981,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Power Corporation of Canada (TSX:POW)</t>
+          <t>Great-West Lifeco Inc. (TSX:GWO)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,121 +990,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0592</v>
+        <v>0.0274</v>
       </c>
       <c r="E5">
-        <v>0.247</v>
+        <v>0.0384</v>
       </c>
       <c r="G5">
-        <v>0.07090492256472757</v>
+        <v>0.09300043082172824</v>
       </c>
       <c r="H5">
-        <v>0.07090492256472757</v>
+        <v>0.09300043082172824</v>
       </c>
       <c r="I5">
-        <v>0.0800808537201629</v>
+        <v>0.06818110490081113</v>
       </c>
       <c r="J5">
-        <v>0.0739249431851139</v>
+        <v>0.06522577483599454</v>
       </c>
       <c r="K5">
-        <v>2345.8</v>
+        <v>2250.6</v>
       </c>
       <c r="L5">
-        <v>0.04358149282125977</v>
+        <v>0.06421240937764805</v>
       </c>
       <c r="M5">
-        <v>1072.5</v>
+        <v>1330</v>
       </c>
       <c r="N5">
-        <v>0.04797348374716521</v>
+        <v>0.06171751013930524</v>
       </c>
       <c r="O5">
-        <v>0.4572001023105124</v>
+        <v>0.5909535235048432</v>
       </c>
       <c r="P5">
-        <v>958.6</v>
+        <v>1330</v>
       </c>
       <c r="Q5">
-        <v>0.04287867740795578</v>
+        <v>0.06171751013930524</v>
       </c>
       <c r="R5">
-        <v>0.4086452382982351</v>
+        <v>0.5909535235048432</v>
       </c>
       <c r="S5">
-        <v>113.9</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.1062004662004662</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>8018.9</v>
+        <v>6290.1</v>
       </c>
       <c r="V5">
-        <v>0.358689574657476</v>
+        <v>0.2918866996445443</v>
       </c>
       <c r="W5">
-        <v>0.1528547039735186</v>
+        <v>0.1175726927939317</v>
       </c>
       <c r="X5">
-        <v>0.07443430430329627</v>
+        <v>0.09827536171421206</v>
       </c>
       <c r="Y5">
-        <v>0.07842039967022231</v>
+        <v>0.01929733107971966</v>
       </c>
       <c r="Z5">
-        <v>3.215311462091706</v>
+        <v>2.227360540932142</v>
       </c>
       <c r="AA5">
-        <v>0.2376917171575749</v>
+        <v>0.1452813171214189</v>
       </c>
       <c r="AB5">
-        <v>0.05219688544495375</v>
+        <v>0.08315401109237466</v>
       </c>
       <c r="AC5">
-        <v>0.1854948317126211</v>
+        <v>0.0621273060290442</v>
       </c>
       <c r="AD5">
-        <v>14830.2</v>
+        <v>7269</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>14830.2</v>
+        <v>7269</v>
       </c>
       <c r="AG5">
-        <v>6811.300000000001</v>
+        <v>978.8999999999996</v>
       </c>
       <c r="AH5">
-        <v>0.3988081632214014</v>
+        <v>0.2522311824225852</v>
       </c>
       <c r="AI5">
-        <v>0.302230935558223</v>
+        <v>0.2414059931387429</v>
       </c>
       <c r="AJ5">
-        <v>0.2335244142432991</v>
+        <v>0.04345124219329121</v>
       </c>
       <c r="AK5">
-        <v>0.1659261099824118</v>
+        <v>0.04109399269552074</v>
       </c>
       <c r="AL5">
-        <v>440.5</v>
+        <v>260.8</v>
       </c>
       <c r="AM5">
-        <v>440.5</v>
+        <v>260.8</v>
       </c>
       <c r="AN5">
-        <v>3.125173852573019</v>
+        <v>2.647894506775463</v>
       </c>
       <c r="AO5">
-        <v>9.785244040862656</v>
+        <v>9.162960122699385</v>
       </c>
       <c r="AP5">
-        <v>1.435347915876428</v>
+        <v>0.3565860410899023</v>
       </c>
       <c r="AQ5">
-        <v>9.785244040862656</v>
+        <v>9.162960122699385</v>
       </c>
     </row>
     <row r="6">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Great-West Lifeco Inc. (TSX:GWO)</t>
+          <t>Manulife Financial Corporation (TSX:MFC)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1124,121 +1124,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0616</v>
+        <v>-0.103</v>
       </c>
       <c r="E6">
-        <v>0.04219999999999999</v>
+        <v>0.128</v>
       </c>
       <c r="G6">
-        <v>0.06165908527664745</v>
+        <v>0.4871250382614019</v>
       </c>
       <c r="H6">
-        <v>0.06165908527664745</v>
+        <v>0.4871250382614019</v>
       </c>
       <c r="I6">
-        <v>0.06986737230887302</v>
+        <v>0.4769156208550148</v>
       </c>
       <c r="J6">
-        <v>0.06820452330509183</v>
+        <v>0.3809113007379005</v>
       </c>
       <c r="K6">
-        <v>2694.6</v>
+        <v>5268.2</v>
       </c>
       <c r="L6">
-        <v>0.05385451725598982</v>
+        <v>0.3359478624630139</v>
       </c>
       <c r="M6">
-        <v>1287.6</v>
+        <v>2815.1</v>
       </c>
       <c r="N6">
-        <v>0.0461316881274318</v>
+        <v>0.08414787978788914</v>
       </c>
       <c r="O6">
-        <v>0.4778445780449788</v>
+        <v>0.5343570859116967</v>
       </c>
       <c r="P6">
-        <v>1287.6</v>
+        <v>1844.9</v>
       </c>
       <c r="Q6">
-        <v>0.0461316881274318</v>
+        <v>0.0551470368444022</v>
       </c>
       <c r="R6">
-        <v>0.4778445780449788</v>
+        <v>0.3501955126988345</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>970.2000000000003</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.3446413981741324</v>
       </c>
       <c r="U6">
-        <v>5449.3</v>
+        <v>15259.8</v>
       </c>
       <c r="V6">
-        <v>0.1952356384846335</v>
+        <v>0.456140036228635</v>
       </c>
       <c r="W6">
-        <v>0.171425299641194</v>
+        <v>0.1309032177910299</v>
       </c>
       <c r="X6">
-        <v>0.06227464419911861</v>
+        <v>0.1057750618228622</v>
       </c>
       <c r="Y6">
-        <v>0.1091506554420754</v>
+        <v>0.02512815596816777</v>
       </c>
       <c r="Z6">
-        <v>3.363480528909176</v>
+        <v>0.3736534479595314</v>
       </c>
       <c r="AA6">
-        <v>0.2294045861202085</v>
+        <v>0.1423288208874665</v>
       </c>
       <c r="AB6">
-        <v>0.05359392238019828</v>
+        <v>0.08240250893063214</v>
       </c>
       <c r="AC6">
-        <v>0.1758106637400102</v>
+        <v>0.05992631195683434</v>
       </c>
       <c r="AD6">
-        <v>6938.6</v>
+        <v>18332.1</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>6938.6</v>
+        <v>18332.1</v>
       </c>
       <c r="AG6">
-        <v>1489.3</v>
+        <v>3072.299999999999</v>
       </c>
       <c r="AH6">
-        <v>0.1990989956958393</v>
+        <v>0.3539951686063689</v>
       </c>
       <c r="AI6">
-        <v>0.2249206621911174</v>
+        <v>0.3089134838011722</v>
       </c>
       <c r="AJ6">
-        <v>0.05065525650749812</v>
+        <v>0.08411153546055601</v>
       </c>
       <c r="AK6">
-        <v>0.05863431995527525</v>
+        <v>0.06969195172851826</v>
       </c>
       <c r="AL6">
-        <v>238.1</v>
+        <v>855.1</v>
       </c>
       <c r="AM6">
-        <v>238.1</v>
+        <v>855.1</v>
       </c>
       <c r="AN6">
-        <v>1.80551652354931</v>
+        <v>2.363297666623695</v>
       </c>
       <c r="AO6">
-        <v>14.68206635867283</v>
+        <v>8.746111565898726</v>
       </c>
       <c r="AP6">
-        <v>0.3875357793390581</v>
+        <v>0.3960680675518885</v>
       </c>
       <c r="AQ6">
-        <v>14.68206635867283</v>
+        <v>8.746111565898726</v>
       </c>
     </row>
     <row r="7">
@@ -1258,121 +1258,121 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0492</v>
+        <v>0.04269999999999999</v>
       </c>
       <c r="E7">
-        <v>0.152</v>
+        <v>0.0801</v>
       </c>
       <c r="G7">
-        <v>0.07535216987176595</v>
+        <v>0.1598821566939302</v>
       </c>
       <c r="H7">
-        <v>0.07535216987176595</v>
+        <v>0.1598821566939302</v>
       </c>
       <c r="I7">
-        <v>0.07835110050794569</v>
+        <v>0.1046464700817908</v>
       </c>
       <c r="J7">
-        <v>0.06157659032848305</v>
+        <v>0.08581674785374398</v>
       </c>
       <c r="K7">
-        <v>644.6</v>
+        <v>594.3</v>
       </c>
       <c r="L7">
-        <v>0.05817007029861118</v>
+        <v>0.07994780456306499</v>
       </c>
       <c r="M7">
-        <v>167.66</v>
+        <v>319.8</v>
       </c>
       <c r="N7">
-        <v>0.02723035195140569</v>
+        <v>0.05193497572145444</v>
       </c>
       <c r="O7">
-        <v>0.2600992863791499</v>
+        <v>0.5381120646138314</v>
       </c>
       <c r="P7">
-        <v>164.5</v>
+        <v>199.6</v>
       </c>
       <c r="Q7">
-        <v>0.026717123321044</v>
+        <v>0.03241470029394092</v>
       </c>
       <c r="R7">
-        <v>0.2551970214086255</v>
+        <v>0.3358573111223288</v>
       </c>
       <c r="S7">
-        <v>3.159999999999997</v>
+        <v>120.2</v>
       </c>
       <c r="T7">
-        <v>0.01884766789932003</v>
+        <v>0.3758599124452783</v>
       </c>
       <c r="U7">
-        <v>996.5</v>
+        <v>479.3</v>
       </c>
       <c r="V7">
-        <v>0.1618456740998197</v>
+        <v>0.07783750426295533</v>
       </c>
       <c r="W7">
-        <v>0.1461081644680176</v>
+        <v>0.114163320975085</v>
       </c>
       <c r="X7">
-        <v>0.06551599149614426</v>
+        <v>0.1000620260220672</v>
       </c>
       <c r="Y7">
-        <v>0.08059217297187332</v>
+        <v>0.01410129495301783</v>
       </c>
       <c r="Z7">
-        <v>2.601571007428467</v>
+        <v>1.397608483116493</v>
       </c>
       <c r="AA7">
-        <v>0.1601958721348816</v>
+        <v>0.1199382147938616</v>
       </c>
       <c r="AB7">
-        <v>0.05334637619152244</v>
+        <v>0.08321817137995775</v>
       </c>
       <c r="AC7">
-        <v>0.1068494959433592</v>
+        <v>0.03672004341390389</v>
       </c>
       <c r="AD7">
-        <v>2210.6</v>
+        <v>2386.1</v>
       </c>
       <c r="AE7">
-        <v>0.7647497065074053</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>2211.364749706507</v>
+        <v>2386.1</v>
       </c>
       <c r="AG7">
-        <v>1214.864749706507</v>
+        <v>1906.8</v>
       </c>
       <c r="AH7">
-        <v>0.2642497537895541</v>
+        <v>0.2792785411643531</v>
       </c>
       <c r="AI7">
-        <v>0.2823403983872446</v>
+        <v>0.3146685305094357</v>
       </c>
       <c r="AJ7">
-        <v>0.1647952467155887</v>
+        <v>0.2364436728873458</v>
       </c>
       <c r="AK7">
-        <v>0.177721848862436</v>
+        <v>0.268427276310603</v>
       </c>
       <c r="AL7">
-        <v>56.9</v>
+        <v>55.4</v>
       </c>
       <c r="AM7">
-        <v>56.9</v>
+        <v>55.4</v>
       </c>
       <c r="AN7">
-        <v>2.089048701314042</v>
+        <v>2.233130556855405</v>
       </c>
       <c r="AO7">
-        <v>15.24780316344464</v>
+        <v>14.04151624548737</v>
       </c>
       <c r="AP7">
-        <v>1.148064610353111</v>
+        <v>1.78455779129621</v>
       </c>
       <c r="AQ7">
-        <v>15.24780316344464</v>
+        <v>14.04151624548737</v>
       </c>
     </row>
     <row r="8">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Manulife Financial Corporation (TSX:MFC)</t>
+          <t>E-L Financial Corporation Limited (TSX:ELF)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1391,122 +1391,101 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="D8">
-        <v>-0.0325</v>
-      </c>
-      <c r="E8">
-        <v>0.159</v>
-      </c>
-      <c r="G8">
-        <v>0.1488539643775992</v>
-      </c>
-      <c r="H8">
-        <v>0.1488539643775992</v>
-      </c>
-      <c r="I8">
-        <v>0.1558175895178405</v>
-      </c>
-      <c r="J8">
-        <v>0.1354647778053857</v>
-      </c>
       <c r="K8">
-        <v>5079.2</v>
-      </c>
-      <c r="L8">
-        <v>0.1144278382798877</v>
+        <v>-254.6</v>
       </c>
       <c r="M8">
-        <v>1720.2</v>
+        <v>128.3888</v>
       </c>
       <c r="N8">
-        <v>0.04647807408608252</v>
+        <v>0.05622456754981388</v>
       </c>
       <c r="O8">
-        <v>0.3386753819499134</v>
+        <v>-0.5042765121759624</v>
       </c>
       <c r="P8">
-        <v>1720.2</v>
+        <v>25.1888</v>
       </c>
       <c r="Q8">
-        <v>0.04647807408608252</v>
+        <v>0.0110307860740092</v>
       </c>
       <c r="R8">
-        <v>0.3386753819499134</v>
+        <v>-0.09893479968578162</v>
       </c>
       <c r="S8">
+        <v>103.2</v>
+      </c>
+      <c r="T8">
+        <v>0.8038084318881398</v>
+      </c>
+      <c r="U8">
+        <v>292.1</v>
+      </c>
+      <c r="V8">
+        <v>0.127917670243048</v>
+      </c>
+      <c r="W8">
+        <v>-0.04778528528528529</v>
+      </c>
+      <c r="X8">
+        <v>0.09424761138201115</v>
+      </c>
+      <c r="Y8">
+        <v>-0.1420328966672964</v>
+      </c>
+      <c r="Z8">
         <v>0</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>17490</v>
-      </c>
-      <c r="V8">
-        <v>0.4725622112344979</v>
-      </c>
-      <c r="W8">
-        <v>0.1390612979090976</v>
-      </c>
-      <c r="X8">
-        <v>0.06807255660219548</v>
-      </c>
-      <c r="Y8">
-        <v>0.07098874130690215</v>
-      </c>
-      <c r="Z8">
-        <v>1.076979068351163</v>
-      </c>
       <c r="AA8">
-        <v>0.1458927301952415</v>
+        <v>-0.07283884276031827</v>
       </c>
       <c r="AB8">
-        <v>0.05307101194214282</v>
+        <v>0.08426788495056968</v>
       </c>
       <c r="AC8">
-        <v>0.09282171825309871</v>
+        <v>-0.157106727710888</v>
       </c>
       <c r="AD8">
-        <v>16520.3</v>
+        <v>511.9</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>16520.3</v>
+        <v>511.9</v>
       </c>
       <c r="AG8">
-        <v>-969.7000000000007</v>
+        <v>219.8</v>
       </c>
       <c r="AH8">
-        <v>0.3086101028743931</v>
+        <v>0.1831222723045002</v>
       </c>
       <c r="AI8">
-        <v>0.27184065029948</v>
+        <v>0.0885686108275516</v>
       </c>
       <c r="AJ8">
-        <v>-0.02690524481636347</v>
+        <v>0.08780409858986137</v>
       </c>
       <c r="AK8">
-        <v>-0.02240423270643687</v>
+        <v>0.04005393979152998</v>
       </c>
       <c r="AL8">
-        <v>819.4</v>
+        <v>21.5</v>
       </c>
       <c r="AM8">
-        <v>819.4</v>
+        <v>21.5</v>
       </c>
       <c r="AN8">
-        <v>2.29235294933881</v>
+        <v>-1.2531211750306</v>
       </c>
       <c r="AO8">
-        <v>8.44081034903588</v>
+        <v>-19.54418604651163</v>
       </c>
       <c r="AP8">
-        <v>-0.1345553443323575</v>
+        <v>-0.5380660954712361</v>
       </c>
       <c r="AQ8">
-        <v>8.44081034903588</v>
+        <v>-19.54418604651163</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/canada/canada_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_insurance_life.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0271</v>
+        <v>-0.003495</v>
       </c>
       <c r="E2">
-        <v>0.0579</v>
+        <v>0.12</v>
       </c>
       <c r="G2">
-        <v>0.1952258814019851</v>
+        <v>0.1685110736283201</v>
       </c>
       <c r="H2">
-        <v>0.1952258814019851</v>
+        <v>0.1685110736283201</v>
       </c>
       <c r="I2">
-        <v>0.145809458657956</v>
+        <v>0.2629144420066539</v>
       </c>
       <c r="J2">
-        <v>0.1287677350607608</v>
+        <v>0.230722700916376</v>
       </c>
       <c r="K2">
-        <v>11772.7</v>
+        <v>17518.1</v>
       </c>
       <c r="L2">
-        <v>0.1029872577030273</v>
+        <v>0.1481114168917748</v>
       </c>
       <c r="M2">
-        <v>6982.2968</v>
+        <v>8021.553</v>
       </c>
       <c r="N2">
-        <v>0.06563049216077001</v>
+        <v>0.06180761519649013</v>
       </c>
       <c r="O2">
-        <v>0.593092221835263</v>
+        <v>0.4579008568280807</v>
       </c>
       <c r="P2">
-        <v>5503.1968</v>
+        <v>5882.723</v>
       </c>
       <c r="Q2">
-        <v>0.05172760837688461</v>
+        <v>0.04532751693986713</v>
       </c>
       <c r="R2">
-        <v>0.4674540929438447</v>
+        <v>0.3358082782950206</v>
       </c>
       <c r="S2">
-        <v>1479.1</v>
+        <v>2138.83</v>
       </c>
       <c r="T2">
-        <v>0.2118357386354588</v>
+        <v>0.2666354009005489</v>
       </c>
       <c r="U2">
-        <v>37387.4</v>
+        <v>35909.3</v>
       </c>
       <c r="V2">
-        <v>0.3514249727412866</v>
+        <v>0.2766880922404082</v>
       </c>
       <c r="W2">
-        <v>0.1158680068845084</v>
+        <v>0.1547589037591908</v>
       </c>
       <c r="X2">
-        <v>0.09916869386813962</v>
+        <v>0.08144115038782533</v>
       </c>
       <c r="Y2">
-        <v>0.01669931301636873</v>
+        <v>0.07331775337136544</v>
       </c>
       <c r="Z2">
-        <v>1.157457106261043</v>
+        <v>1.244394901912099</v>
       </c>
       <c r="AA2">
-        <v>0.1438050690044427</v>
+        <v>0.2190199846795987</v>
       </c>
       <c r="AB2">
-        <v>0.08318609123616622</v>
+        <v>0.072067792011742</v>
       </c>
       <c r="AC2">
-        <v>0.06102680899293927</v>
+        <v>0.1481904009274425</v>
       </c>
       <c r="AD2">
-        <v>50301.4</v>
+        <v>49778.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>50301.4</v>
+        <v>49778.5</v>
       </c>
       <c r="AG2">
-        <v>12914</v>
+        <v>13869.2</v>
       </c>
       <c r="AH2">
-        <v>0.3210261830091889</v>
+        <v>0.2772231847543817</v>
       </c>
       <c r="AI2">
-        <v>0.2843646210508761</v>
+        <v>0.2982609508447786</v>
       </c>
       <c r="AJ2">
-        <v>0.1082462993076394</v>
+        <v>0.09654734573461667</v>
       </c>
       <c r="AK2">
-        <v>0.0925714195598521</v>
+        <v>0.105882667297775</v>
       </c>
       <c r="AL2">
-        <v>1907.3</v>
+        <v>3793.4</v>
       </c>
       <c r="AM2">
-        <v>1907.3</v>
+        <v>3793.4</v>
       </c>
       <c r="AN2">
-        <v>2.739280074061972</v>
+        <v>1.518044475347045</v>
       </c>
       <c r="AO2">
-        <v>8.73895034866041</v>
+        <v>8.197553645805874</v>
       </c>
       <c r="AP2">
-        <v>0.7032619942275228</v>
+        <v>0.4229549391300106</v>
       </c>
       <c r="AQ2">
-        <v>8.73895034866041</v>
+        <v>8.197553645805874</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Power Corporation of Canada (TSX:POW)</t>
+          <t>iA Financial Corporation Inc. (TSX:IAG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,121 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0271</v>
+        <v>0.0931</v>
       </c>
       <c r="E3">
-        <v>0.0579</v>
+        <v>0.149</v>
       </c>
       <c r="G3">
-        <v>0.1215302389834279</v>
+        <v>0.08740096709666241</v>
       </c>
       <c r="H3">
-        <v>0.1215302389834279</v>
+        <v>0.08740096709666241</v>
       </c>
       <c r="I3">
-        <v>0.08380976525918758</v>
+        <v>0.5395029060152152</v>
       </c>
       <c r="J3">
-        <v>0.07504304142086674</v>
+        <v>0.4302711513105859</v>
       </c>
       <c r="K3">
-        <v>1533.2</v>
+        <v>911.5</v>
       </c>
       <c r="L3">
-        <v>0.03966328119745236</v>
+        <v>0.0717840885822741</v>
       </c>
       <c r="M3">
-        <v>1233.8</v>
+        <v>476.8</v>
       </c>
       <c r="N3">
-        <v>0.07852496785937042</v>
+        <v>0.06986182947735499</v>
       </c>
       <c r="O3">
-        <v>0.8047221497521523</v>
+        <v>0.5230938014262205</v>
       </c>
       <c r="P3">
-        <v>948.3</v>
+        <v>220.3</v>
       </c>
       <c r="Q3">
-        <v>0.06035437430786268</v>
+        <v>0.03227886122873595</v>
       </c>
       <c r="R3">
-        <v>0.6185103052439342</v>
+        <v>0.2416895227646736</v>
       </c>
       <c r="S3">
-        <v>285.5</v>
+        <v>256.5</v>
       </c>
       <c r="T3">
-        <v>0.2313989301345437</v>
+        <v>0.5379614093959731</v>
       </c>
       <c r="U3">
-        <v>8222.4</v>
+        <v>475.3</v>
       </c>
       <c r="V3">
-        <v>0.523313094283423</v>
+        <v>0.06964204603730458</v>
       </c>
       <c r="W3">
-        <v>0.08412019993086914</v>
+        <v>0.1893239173330564</v>
       </c>
       <c r="X3">
-        <v>0.1189353155788761</v>
+        <v>0.08249048978986759</v>
       </c>
       <c r="Y3">
-        <v>-0.03481511564800695</v>
+        <v>0.1068334275431888</v>
       </c>
       <c r="Z3">
-        <v>2.482477378253582</v>
+        <v>2.206777893639207</v>
       </c>
       <c r="AA3">
-        <v>0.1862926527226482</v>
+        <v>0.9495128649828916</v>
       </c>
       <c r="AB3">
-        <v>0.0803611296377883</v>
+        <v>0.07186744924025158</v>
       </c>
       <c r="AC3">
-        <v>0.1059315230848599</v>
+        <v>0.87764541574264</v>
       </c>
       <c r="AD3">
-        <v>14418.2</v>
+        <v>2044</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>14418.2</v>
+        <v>2044</v>
       </c>
       <c r="AG3">
-        <v>6195.800000000001</v>
+        <v>1568.7</v>
       </c>
       <c r="AH3">
-        <v>0.4785266707378594</v>
+        <v>0.2304682655120703</v>
       </c>
       <c r="AI3">
-        <v>0.3153373240222119</v>
+        <v>0.2830397695801484</v>
       </c>
       <c r="AJ3">
-        <v>0.2828099324447691</v>
+        <v>0.1868923942051086</v>
       </c>
       <c r="AK3">
-        <v>0.1652182492593472</v>
+        <v>0.2325274594963165</v>
       </c>
       <c r="AL3">
-        <v>423.2</v>
+        <v>432.5</v>
       </c>
       <c r="AM3">
-        <v>423.2</v>
+        <v>432.5</v>
       </c>
       <c r="AN3">
-        <v>3.875339336110738</v>
+        <v>0.2851721636252023</v>
       </c>
       <c r="AO3">
-        <v>7.655245746691871</v>
+        <v>15.8393063583815</v>
       </c>
       <c r="AP3">
-        <v>1.665313801908346</v>
+        <v>0.2188598694123556</v>
       </c>
       <c r="AQ3">
-        <v>7.655245746691871</v>
+        <v>15.8393063583815</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sun Life Financial Inc. (TSX:SLF)</t>
+          <t>Manulife Financial Corporation (TSX:MFC)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,121 +856,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.008229999999999999</v>
+        <v>-0.152</v>
       </c>
       <c r="E4">
-        <v>0.0342</v>
+        <v>0.395</v>
       </c>
       <c r="G4">
-        <v>0.2465198973262521</v>
+        <v>0.527153532422741</v>
       </c>
       <c r="H4">
-        <v>0.2465198973262521</v>
+        <v>0.527153532422741</v>
       </c>
       <c r="I4">
-        <v>0.1830462546377549</v>
+        <v>0.9478416773875673</v>
       </c>
       <c r="J4">
-        <v>0.1515489359592129</v>
+        <v>0.7785203295216093</v>
       </c>
       <c r="K4">
-        <v>2381</v>
+        <v>10256.1</v>
       </c>
       <c r="L4">
-        <v>0.1361170343522579</v>
+        <v>0.7018380642159143</v>
       </c>
       <c r="M4">
-        <v>1155.208</v>
+        <v>3284.4</v>
       </c>
       <c r="N4">
-        <v>0.04242315630210131</v>
+        <v>0.08200196241451888</v>
       </c>
       <c r="O4">
-        <v>0.485177656446871</v>
+        <v>0.3202386872202884</v>
       </c>
       <c r="P4">
-        <v>1155.208</v>
+        <v>1943.4</v>
       </c>
       <c r="Q4">
-        <v>0.04242315630210131</v>
+        <v>0.04852107348568262</v>
       </c>
       <c r="R4">
-        <v>0.485177656446871</v>
+        <v>0.1894872319887677</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1341</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.4082937522835221</v>
       </c>
       <c r="U4">
-        <v>6843.7</v>
+        <v>16364.4</v>
       </c>
       <c r="V4">
-        <v>0.2513238782839893</v>
+        <v>0.4085717067763222</v>
       </c>
       <c r="W4">
-        <v>0.1203808098529241</v>
+        <v>0.2699961301634019</v>
       </c>
       <c r="X4">
-        <v>0.09592067239384906</v>
+        <v>0.08811419881264031</v>
       </c>
       <c r="Y4">
-        <v>0.02446013745907501</v>
+        <v>0.1818819313507616</v>
       </c>
       <c r="Z4">
-        <v>1.214878042004667</v>
+        <v>0.3408040374452525</v>
       </c>
       <c r="AA4">
-        <v>0.1841134745860192</v>
+        <v>0.2653228715341729</v>
       </c>
       <c r="AB4">
-        <v>0.08363421015314147</v>
+        <v>0.07057519833586945</v>
       </c>
       <c r="AC4">
-        <v>0.1004792644328777</v>
+        <v>0.1947476731983034</v>
       </c>
       <c r="AD4">
-        <v>7384.1</v>
+        <v>20553.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>7384.1</v>
+        <v>20553.7</v>
       </c>
       <c r="AG4">
-        <v>540.4000000000005</v>
+        <v>4189.300000000001</v>
       </c>
       <c r="AH4">
-        <v>0.213322663492678</v>
+        <v>0.3391341508487553</v>
       </c>
       <c r="AI4">
-        <v>0.2604629998694881</v>
+        <v>0.361847537326965</v>
       </c>
       <c r="AJ4">
-        <v>0.01945914803211986</v>
+        <v>0.09469056552597083</v>
       </c>
       <c r="AK4">
-        <v>0.0251276376114795</v>
+        <v>0.103598869371898</v>
       </c>
       <c r="AL4">
-        <v>291.3</v>
+        <v>1330.6</v>
       </c>
       <c r="AM4">
-        <v>291.3</v>
+        <v>1330.6</v>
       </c>
       <c r="AN4">
-        <v>2.121684912220211</v>
+        <v>1.473668738752304</v>
       </c>
       <c r="AO4">
-        <v>10.99176107106076</v>
+        <v>10.40958965880054</v>
       </c>
       <c r="AP4">
-        <v>0.1552739706347155</v>
+        <v>0.3003663791558224</v>
       </c>
       <c r="AQ4">
-        <v>10.99176107106076</v>
+        <v>10.40958965880054</v>
       </c>
     </row>
     <row r="5">
@@ -981,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Great-West Lifeco Inc. (TSX:GWO)</t>
+          <t>Power Corporation of Canada (TSX:POW)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,121 +990,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0274</v>
+        <v>0.00224</v>
       </c>
       <c r="E5">
-        <v>0.0384</v>
+        <v>0.0457</v>
       </c>
       <c r="G5">
-        <v>0.09300043082172824</v>
+        <v>0.1133444882049397</v>
       </c>
       <c r="H5">
-        <v>0.09300043082172824</v>
+        <v>0.1133444882049397</v>
       </c>
       <c r="I5">
-        <v>0.06818110490081113</v>
+        <v>0.08276680461584622</v>
       </c>
       <c r="J5">
-        <v>0.06522577483599454</v>
+        <v>0.07669559212037975</v>
       </c>
       <c r="K5">
-        <v>2250.6</v>
+        <v>1218.3</v>
       </c>
       <c r="L5">
-        <v>0.06421240937764805</v>
+        <v>0.03293210035059455</v>
       </c>
       <c r="M5">
-        <v>1330</v>
+        <v>1278.9</v>
       </c>
       <c r="N5">
-        <v>0.06171751013930524</v>
+        <v>0.06809287764153404</v>
       </c>
       <c r="O5">
-        <v>0.5909535235048432</v>
+        <v>1.049741442994337</v>
       </c>
       <c r="P5">
-        <v>1330</v>
+        <v>1004.6</v>
       </c>
       <c r="Q5">
-        <v>0.06171751013930524</v>
+        <v>0.05348823588919001</v>
       </c>
       <c r="R5">
-        <v>0.5909535235048432</v>
+        <v>0.8245916440942297</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>274.3000000000001</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.2144811947767613</v>
       </c>
       <c r="U5">
-        <v>6290.1</v>
+        <v>7030.9</v>
       </c>
       <c r="V5">
-        <v>0.2918866996445443</v>
+        <v>0.3743484349127075</v>
       </c>
       <c r="W5">
-        <v>0.1175726927939317</v>
+        <v>0.07495708563799351</v>
       </c>
       <c r="X5">
-        <v>0.09827536171421206</v>
+        <v>0.09593416297785629</v>
       </c>
       <c r="Y5">
-        <v>0.01929733107971966</v>
+        <v>-0.02097707733986277</v>
       </c>
       <c r="Z5">
-        <v>2.227360540932142</v>
+        <v>2.932448178827633</v>
       </c>
       <c r="AA5">
-        <v>0.1452813171214189</v>
+        <v>0.2249058494375146</v>
       </c>
       <c r="AB5">
-        <v>0.08315401109237466</v>
+        <v>0.06879445403685272</v>
       </c>
       <c r="AC5">
-        <v>0.0621273060290442</v>
+        <v>0.1561113954006619</v>
       </c>
       <c r="AD5">
-        <v>7269</v>
+        <v>15218.6</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>7269</v>
+        <v>15218.6</v>
       </c>
       <c r="AG5">
-        <v>978.8999999999996</v>
+        <v>8187.700000000001</v>
       </c>
       <c r="AH5">
-        <v>0.2522311824225852</v>
+        <v>0.4476019329241212</v>
       </c>
       <c r="AI5">
-        <v>0.2414059931387429</v>
+        <v>0.332842698767144</v>
       </c>
       <c r="AJ5">
-        <v>0.04345124219329121</v>
+        <v>0.3035922193300555</v>
       </c>
       <c r="AK5">
-        <v>0.04109399269552074</v>
+        <v>0.2116111257566125</v>
       </c>
       <c r="AL5">
-        <v>260.8</v>
+        <v>913</v>
       </c>
       <c r="AM5">
-        <v>260.8</v>
+        <v>913</v>
       </c>
       <c r="AN5">
-        <v>2.647894506775463</v>
+        <v>4.202291868010493</v>
       </c>
       <c r="AO5">
-        <v>9.162960122699385</v>
+        <v>3.353669222343921</v>
       </c>
       <c r="AP5">
-        <v>0.3565860410899023</v>
+        <v>2.260858760182245</v>
       </c>
       <c r="AQ5">
-        <v>9.162960122699385</v>
+        <v>3.353669222343921</v>
       </c>
     </row>
     <row r="6">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Manulife Financial Corporation (TSX:MFC)</t>
+          <t>Sun Life Financial Inc. (TSX:SLF)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1124,121 +1124,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.103</v>
+        <v>-0.007860000000000001</v>
       </c>
       <c r="E6">
-        <v>0.128</v>
+        <v>0.109</v>
       </c>
       <c r="G6">
-        <v>0.4871250382614019</v>
+        <v>0.1837959143938967</v>
       </c>
       <c r="H6">
-        <v>0.4871250382614019</v>
+        <v>0.1837959143938967</v>
       </c>
       <c r="I6">
-        <v>0.4769156208550148</v>
+        <v>0.1900621499900089</v>
       </c>
       <c r="J6">
-        <v>0.3809113007379005</v>
+        <v>0.1661485807141575</v>
       </c>
       <c r="K6">
-        <v>5268.2</v>
+        <v>2786.9</v>
       </c>
       <c r="L6">
-        <v>0.3359478624630139</v>
+        <v>0.1427912672347097</v>
       </c>
       <c r="M6">
-        <v>2815.1</v>
+        <v>1405.431</v>
       </c>
       <c r="N6">
-        <v>0.08414787978788914</v>
+        <v>0.04622292019535939</v>
       </c>
       <c r="O6">
-        <v>0.5343570859116967</v>
+        <v>0.5042990419462484</v>
       </c>
       <c r="P6">
-        <v>1844.9</v>
+        <v>1267.931</v>
       </c>
       <c r="Q6">
-        <v>0.0551470368444022</v>
+        <v>0.04170071204222919</v>
       </c>
       <c r="R6">
-        <v>0.3501955126988345</v>
+        <v>0.4549610678531701</v>
       </c>
       <c r="S6">
-        <v>970.2000000000003</v>
+        <v>137.5</v>
       </c>
       <c r="T6">
-        <v>0.3446413981741324</v>
+        <v>0.09783475674010322</v>
       </c>
       <c r="U6">
-        <v>15259.8</v>
+        <v>6605.8</v>
       </c>
       <c r="V6">
-        <v>0.456140036228635</v>
+        <v>0.2172567463123448</v>
       </c>
       <c r="W6">
-        <v>0.1309032177910299</v>
+        <v>0.1444858049397565</v>
       </c>
       <c r="X6">
-        <v>0.1057750618228622</v>
+        <v>0.07868869536477927</v>
       </c>
       <c r="Y6">
-        <v>0.02512815596816777</v>
+        <v>0.06579710957497725</v>
       </c>
       <c r="Z6">
-        <v>0.3736534479595314</v>
+        <v>1.282792299552406</v>
       </c>
       <c r="AA6">
-        <v>0.1423288208874665</v>
+        <v>0.2131341199216827</v>
       </c>
       <c r="AB6">
-        <v>0.08240250893063214</v>
+        <v>0.07286471346745965</v>
       </c>
       <c r="AC6">
-        <v>0.05992631195683434</v>
+        <v>0.140269406454223</v>
       </c>
       <c r="AD6">
-        <v>18332.1</v>
+        <v>4714.1</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>18332.1</v>
+        <v>4714.1</v>
       </c>
       <c r="AG6">
-        <v>3072.299999999999</v>
+        <v>-1891.7</v>
       </c>
       <c r="AH6">
-        <v>0.3539951686063689</v>
+        <v>0.1342298887231062</v>
       </c>
       <c r="AI6">
-        <v>0.3089134838011722</v>
+        <v>0.2115511477101892</v>
       </c>
       <c r="AJ6">
-        <v>0.08411153546055601</v>
+        <v>-0.06634331446527646</v>
       </c>
       <c r="AK6">
-        <v>0.06969195172851826</v>
+        <v>-0.1206618317737933</v>
       </c>
       <c r="AL6">
-        <v>855.1</v>
+        <v>416.9</v>
       </c>
       <c r="AM6">
-        <v>855.1</v>
+        <v>416.9</v>
       </c>
       <c r="AN6">
-        <v>2.363297666623695</v>
+        <v>1.164751809848541</v>
       </c>
       <c r="AO6">
-        <v>8.746111565898726</v>
+        <v>8.897817222355481</v>
       </c>
       <c r="AP6">
-        <v>0.3960680675518885</v>
+        <v>-0.467398018432041</v>
       </c>
       <c r="AQ6">
-        <v>8.746111565898726</v>
+        <v>8.897817222355481</v>
       </c>
     </row>
     <row r="7">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>iA Financial Corporation Inc. (TSX:IAG)</t>
+          <t>Great-West Lifeco Inc. (TSX:GWO)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1258,121 +1258,121 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.04269999999999999</v>
+        <v>0.0008699999999999999</v>
       </c>
       <c r="E7">
-        <v>0.0801</v>
+        <v>-0.0452</v>
       </c>
       <c r="G7">
-        <v>0.1598821566939302</v>
+        <v>0.1062784966845633</v>
       </c>
       <c r="H7">
-        <v>0.1598821566939302</v>
+        <v>0.1062784966845633</v>
       </c>
       <c r="I7">
-        <v>0.1046464700817908</v>
+        <v>0.07731157962405208</v>
       </c>
       <c r="J7">
-        <v>0.08581674785374398</v>
+        <v>0.07706355474316068</v>
       </c>
       <c r="K7">
-        <v>594.3</v>
+        <v>1628.5</v>
       </c>
       <c r="L7">
-        <v>0.07994780456306499</v>
+        <v>0.04846668492041761</v>
       </c>
       <c r="M7">
-        <v>319.8</v>
+        <v>1537.6</v>
       </c>
       <c r="N7">
-        <v>0.05193497572145444</v>
+        <v>0.04964516108201655</v>
       </c>
       <c r="O7">
-        <v>0.5381120646138314</v>
+        <v>0.9441817623579982</v>
       </c>
       <c r="P7">
-        <v>199.6</v>
+        <v>1411.2</v>
       </c>
       <c r="Q7">
-        <v>0.03241470029394092</v>
+        <v>0.04556402921367179</v>
       </c>
       <c r="R7">
-        <v>0.3358573111223288</v>
+        <v>0.8665643229966227</v>
       </c>
       <c r="S7">
-        <v>120.2</v>
+        <v>126.4000000000001</v>
       </c>
       <c r="T7">
-        <v>0.3758599124452783</v>
+        <v>0.08220603537981275</v>
       </c>
       <c r="U7">
-        <v>479.3</v>
+        <v>5158.4</v>
       </c>
       <c r="V7">
-        <v>0.07783750426295533</v>
+        <v>0.16655150814612</v>
       </c>
       <c r="W7">
-        <v>0.114163320975085</v>
+        <v>0.08813326333905193</v>
       </c>
       <c r="X7">
-        <v>0.1000620260220672</v>
+        <v>0.08039181098578307</v>
       </c>
       <c r="Y7">
-        <v>0.01410129495301783</v>
+        <v>0.007741452353268855</v>
       </c>
       <c r="Z7">
-        <v>1.397608483116493</v>
+        <v>2.431200028942514</v>
       </c>
       <c r="AA7">
-        <v>0.1199382147938616</v>
+        <v>0.1873569165219852</v>
       </c>
       <c r="AB7">
-        <v>0.08321817137995775</v>
+        <v>0.07226813478323242</v>
       </c>
       <c r="AC7">
-        <v>0.03672004341390389</v>
+        <v>0.1150887817387528</v>
       </c>
       <c r="AD7">
-        <v>2386.1</v>
+        <v>6806.1</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>2386.1</v>
+        <v>6806.1</v>
       </c>
       <c r="AG7">
-        <v>1906.8</v>
+        <v>1647.700000000001</v>
       </c>
       <c r="AH7">
-        <v>0.2792785411643531</v>
+        <v>0.180160887714775</v>
       </c>
       <c r="AI7">
-        <v>0.3146685305094357</v>
+        <v>0.2376846516500786</v>
       </c>
       <c r="AJ7">
-        <v>0.2364436728873458</v>
+        <v>0.05051273011542178</v>
       </c>
       <c r="AK7">
-        <v>0.268427276310603</v>
+        <v>0.07018477973812225</v>
       </c>
       <c r="AL7">
-        <v>55.4</v>
+        <v>640.9</v>
       </c>
       <c r="AM7">
-        <v>55.4</v>
+        <v>640.9</v>
       </c>
       <c r="AN7">
-        <v>2.233130556855405</v>
+        <v>2.287457148618673</v>
       </c>
       <c r="AO7">
-        <v>14.04151624548737</v>
+        <v>4.053206428459978</v>
       </c>
       <c r="AP7">
-        <v>1.78455779129621</v>
+        <v>0.5537742824494188</v>
       </c>
       <c r="AQ7">
-        <v>14.04151624548737</v>
+        <v>4.053206428459978</v>
       </c>
     </row>
     <row r="8">
@@ -1391,101 +1391,122 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
+      <c r="D8">
+        <v>-0.105</v>
+      </c>
+      <c r="E8">
+        <v>0.131</v>
+      </c>
+      <c r="G8">
+        <v>-0.2736965436438196</v>
+      </c>
+      <c r="H8">
+        <v>-0.2736965436438196</v>
+      </c>
+      <c r="I8">
+        <v>1.202108963093146</v>
+      </c>
+      <c r="J8">
+        <v>1.020393371258786</v>
+      </c>
       <c r="K8">
-        <v>-254.6</v>
+        <v>716.8</v>
+      </c>
+      <c r="L8">
+        <v>0.8398359695371997</v>
       </c>
       <c r="M8">
-        <v>128.3888</v>
+        <v>38.422</v>
       </c>
       <c r="N8">
-        <v>0.05622456754981388</v>
+        <v>0.01399198834668609</v>
       </c>
       <c r="O8">
-        <v>-0.5042765121759624</v>
+        <v>0.05360212053571428</v>
       </c>
       <c r="P8">
-        <v>25.1888</v>
+        <v>35.29199999999999</v>
       </c>
       <c r="Q8">
-        <v>0.0110307860740092</v>
+        <v>0.01285214857975236</v>
       </c>
       <c r="R8">
-        <v>-0.09893479968578162</v>
+        <v>0.04923549107142856</v>
       </c>
       <c r="S8">
-        <v>103.2</v>
+        <v>3.130000000000003</v>
       </c>
       <c r="T8">
-        <v>0.8038084318881398</v>
+        <v>0.08146374472958208</v>
       </c>
       <c r="U8">
-        <v>292.1</v>
+        <v>274.5</v>
       </c>
       <c r="V8">
-        <v>0.127917670243048</v>
+        <v>0.09996358339402768</v>
       </c>
       <c r="W8">
-        <v>-0.04778528528528529</v>
+        <v>0.165032002578625</v>
       </c>
       <c r="X8">
-        <v>0.09424761138201115</v>
+        <v>0.07884451360161396</v>
       </c>
       <c r="Y8">
-        <v>-0.1420328966672964</v>
+        <v>0.08618748897701109</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>0.1791524107386495</v>
       </c>
       <c r="AA8">
-        <v>-0.07283884276031827</v>
+        <v>0.1828059323627494</v>
       </c>
       <c r="AB8">
-        <v>0.08426788495056968</v>
+        <v>0.07295940926914427</v>
       </c>
       <c r="AC8">
-        <v>-0.157106727710888</v>
+        <v>0.1098465230936051</v>
       </c>
       <c r="AD8">
-        <v>511.9</v>
+        <v>442</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>511.9</v>
+        <v>442</v>
       </c>
       <c r="AG8">
-        <v>219.8</v>
+        <v>167.5</v>
       </c>
       <c r="AH8">
-        <v>0.1831222723045002</v>
+        <v>0.1386449184441656</v>
       </c>
       <c r="AI8">
-        <v>0.0885686108275516</v>
+        <v>0.07094133697135062</v>
       </c>
       <c r="AJ8">
-        <v>0.08780409858986137</v>
+        <v>0.05749099021795092</v>
       </c>
       <c r="AK8">
-        <v>0.04005393979152998</v>
+        <v>0.02812290127602418</v>
       </c>
       <c r="AL8">
-        <v>21.5</v>
+        <v>59.5</v>
       </c>
       <c r="AM8">
-        <v>21.5</v>
+        <v>59.5</v>
       </c>
       <c r="AN8">
-        <v>-1.2531211750306</v>
+        <v>0.4282530762523012</v>
       </c>
       <c r="AO8">
-        <v>-19.54418604651163</v>
+        <v>17.2436974789916</v>
       </c>
       <c r="AP8">
-        <v>-0.5380660954712361</v>
+        <v>0.162290475729096</v>
       </c>
       <c r="AQ8">
-        <v>-19.54418604651163</v>
+        <v>17.2436974789916</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/canada/canada_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_insurance_life.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.003495</v>
+        <v>-0.06494999999999999</v>
       </c>
       <c r="E2">
-        <v>0.12</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="G2">
-        <v>0.1685110736283201</v>
+        <v>0.200941416896292</v>
       </c>
       <c r="H2">
-        <v>0.1685110736283201</v>
+        <v>0.200941416896292</v>
       </c>
       <c r="I2">
-        <v>0.2629144420066539</v>
+        <v>0.2171729693889243</v>
       </c>
       <c r="J2">
-        <v>0.230722700916376</v>
+        <v>0.1846701606364075</v>
       </c>
       <c r="K2">
-        <v>17518.1</v>
+        <v>13406.3</v>
       </c>
       <c r="L2">
-        <v>0.1481114168917748</v>
+        <v>0.125906996575812</v>
       </c>
       <c r="M2">
-        <v>8021.553</v>
+        <v>9442.361999999999</v>
       </c>
       <c r="N2">
-        <v>0.06180761519649013</v>
+        <v>0.06267801846282112</v>
       </c>
       <c r="O2">
-        <v>0.4579008568280807</v>
+        <v>0.7043227437846385</v>
       </c>
       <c r="P2">
-        <v>5882.723</v>
+        <v>6259.262</v>
       </c>
       <c r="Q2">
-        <v>0.04532751693986713</v>
+        <v>0.04154872893028616</v>
       </c>
       <c r="R2">
-        <v>0.3358082782950206</v>
+        <v>0.4668895966821569</v>
       </c>
       <c r="S2">
-        <v>2138.83</v>
+        <v>3183.099999999999</v>
       </c>
       <c r="T2">
-        <v>0.2666354009005489</v>
+        <v>0.3371084480768688</v>
       </c>
       <c r="U2">
-        <v>35909.3</v>
+        <v>41314.8</v>
       </c>
       <c r="V2">
-        <v>0.2766880922404082</v>
+        <v>0.2742459775623687</v>
       </c>
       <c r="W2">
-        <v>0.1547589037591908</v>
+        <v>0.1523486789691678</v>
       </c>
       <c r="X2">
-        <v>0.08144115038782533</v>
+        <v>0.08632964769837134</v>
       </c>
       <c r="Y2">
-        <v>0.07331775337136544</v>
+        <v>0.06601903127079642</v>
       </c>
       <c r="Z2">
-        <v>1.244394901912099</v>
+        <v>1.237234941221992</v>
       </c>
       <c r="AA2">
-        <v>0.2190199846795987</v>
+        <v>0.2828313839305208</v>
       </c>
       <c r="AB2">
-        <v>0.072067792011742</v>
+        <v>0.07627370865121047</v>
       </c>
       <c r="AC2">
-        <v>0.1481904009274425</v>
+        <v>0.2075505529274719</v>
       </c>
       <c r="AD2">
-        <v>49778.5</v>
+        <v>50253.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>49778.5</v>
+        <v>50253.4</v>
       </c>
       <c r="AG2">
-        <v>13869.2</v>
+        <v>8938.599999999999</v>
       </c>
       <c r="AH2">
-        <v>0.2772231847543817</v>
+        <v>0.2501387491718604</v>
       </c>
       <c r="AI2">
-        <v>0.2982609508447786</v>
+        <v>0.2876256094817881</v>
       </c>
       <c r="AJ2">
-        <v>0.09654734573461667</v>
+        <v>0.05601072265775534</v>
       </c>
       <c r="AK2">
-        <v>0.105882667297775</v>
+        <v>0.06700433947286161</v>
       </c>
       <c r="AL2">
-        <v>3793.4</v>
+        <v>5250</v>
       </c>
       <c r="AM2">
-        <v>3793.4</v>
+        <v>5250</v>
       </c>
       <c r="AN2">
-        <v>1.518044475347045</v>
+        <v>2.797855401026646</v>
       </c>
       <c r="AO2">
-        <v>8.197553645805874</v>
+        <v>4.404590476190476</v>
       </c>
       <c r="AP2">
-        <v>0.4229549391300106</v>
+        <v>0.4976560847149998</v>
       </c>
       <c r="AQ2">
-        <v>8.197553645805874</v>
+        <v>4.404590476190476</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>iA Financial Corporation Inc. (TSX:IAG)</t>
+          <t>Great-West Lifeco Inc. (TSX:GWO)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,121 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0931</v>
+        <v>-0.0614</v>
       </c>
       <c r="E3">
-        <v>0.149</v>
+        <v>0.06559999999999999</v>
       </c>
       <c r="G3">
-        <v>0.08740096709666241</v>
+        <v>0.2335902011680727</v>
       </c>
       <c r="H3">
-        <v>0.08740096709666241</v>
+        <v>0.2335902011680727</v>
       </c>
       <c r="I3">
-        <v>0.5395029060152152</v>
+        <v>0.2490914990266061</v>
       </c>
       <c r="J3">
-        <v>0.4302711513105859</v>
+        <v>0.2278030654033409</v>
       </c>
       <c r="K3">
-        <v>911.5</v>
+        <v>2734.4</v>
       </c>
       <c r="L3">
-        <v>0.0717840885822741</v>
+        <v>0.1109020116807268</v>
       </c>
       <c r="M3">
-        <v>476.8</v>
+        <v>1638.1</v>
       </c>
       <c r="N3">
-        <v>0.06986182947735499</v>
+        <v>0.05306222931978893</v>
       </c>
       <c r="O3">
-        <v>0.5230938014262205</v>
+        <v>0.5990710942071387</v>
       </c>
       <c r="P3">
-        <v>220.3</v>
+        <v>1507.1</v>
       </c>
       <c r="Q3">
-        <v>0.03227886122873595</v>
+        <v>0.04881880581640553</v>
       </c>
       <c r="R3">
-        <v>0.2416895227646736</v>
+        <v>0.551162960795787</v>
       </c>
       <c r="S3">
-        <v>256.5</v>
+        <v>131</v>
       </c>
       <c r="T3">
-        <v>0.5379614093959731</v>
+        <v>0.07997069775959954</v>
       </c>
       <c r="U3">
-        <v>475.3</v>
+        <v>6578.3</v>
       </c>
       <c r="V3">
-        <v>0.06964204603730458</v>
+        <v>0.2130878842160842</v>
       </c>
       <c r="W3">
-        <v>0.1893239173330564</v>
+        <v>0.1548524473187942</v>
       </c>
       <c r="X3">
-        <v>0.08249048978986759</v>
+        <v>0.08494432910377495</v>
       </c>
       <c r="Y3">
-        <v>0.1068334275431888</v>
+        <v>0.06990811821501927</v>
       </c>
       <c r="Z3">
-        <v>2.206777893639207</v>
+        <v>1.843866615813759</v>
       </c>
       <c r="AA3">
-        <v>0.9495128649828916</v>
+        <v>0.4200384672772585</v>
       </c>
       <c r="AB3">
-        <v>0.07186744924025158</v>
+        <v>0.07676395269355669</v>
       </c>
       <c r="AC3">
-        <v>0.87764541574264</v>
+        <v>0.3432745145837018</v>
       </c>
       <c r="AD3">
-        <v>2044</v>
+        <v>6744.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2044</v>
+        <v>6744.9</v>
       </c>
       <c r="AG3">
-        <v>1568.7</v>
+        <v>166.5999999999995</v>
       </c>
       <c r="AH3">
-        <v>0.2304682655120703</v>
+        <v>0.1793083830902643</v>
       </c>
       <c r="AI3">
-        <v>0.2830397695801484</v>
+        <v>0.2254168351608688</v>
       </c>
       <c r="AJ3">
-        <v>0.1868923942051086</v>
+        <v>0.005367631186388237</v>
       </c>
       <c r="AK3">
-        <v>0.2325274594963165</v>
+        <v>0.007136859781696031</v>
       </c>
       <c r="AL3">
-        <v>432.5</v>
+        <v>2819.5</v>
       </c>
       <c r="AM3">
-        <v>432.5</v>
+        <v>2819.5</v>
       </c>
       <c r="AN3">
-        <v>0.2851721636252023</v>
+        <v>1.038875625721987</v>
       </c>
       <c r="AO3">
-        <v>15.8393063583815</v>
+        <v>2.178258556481646</v>
       </c>
       <c r="AP3">
-        <v>0.2188598694123556</v>
+        <v>0.02566037735849048</v>
       </c>
       <c r="AQ3">
-        <v>15.8393063583815</v>
+        <v>2.178258556481646</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Manulife Financial Corporation (TSX:MFC)</t>
+          <t>Sun Life Financial Inc. (TSX:SLF)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,121 +856,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.152</v>
+        <v>-0.0371</v>
       </c>
       <c r="E4">
-        <v>0.395</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="G4">
-        <v>0.527153532422741</v>
+        <v>0.1457213038571334</v>
       </c>
       <c r="H4">
-        <v>0.527153532422741</v>
+        <v>0.1457213038571334</v>
       </c>
       <c r="I4">
-        <v>0.9478416773875673</v>
+        <v>0.1468706432981478</v>
       </c>
       <c r="J4">
-        <v>0.7785203295216093</v>
+        <v>0.1271303108973561</v>
       </c>
       <c r="K4">
-        <v>10256.1</v>
+        <v>2695.1</v>
       </c>
       <c r="L4">
-        <v>0.7018380642159143</v>
+        <v>0.1118261634468565</v>
       </c>
       <c r="M4">
-        <v>3284.4</v>
+        <v>1800.555</v>
       </c>
       <c r="N4">
-        <v>0.08200196241451888</v>
+        <v>0.05275934211798627</v>
       </c>
       <c r="O4">
-        <v>0.3202386872202884</v>
+        <v>0.6680846721828503</v>
       </c>
       <c r="P4">
-        <v>1943.4</v>
+        <v>1351.955</v>
       </c>
       <c r="Q4">
-        <v>0.04852107348568262</v>
+        <v>0.03961459459617847</v>
       </c>
       <c r="R4">
-        <v>0.1894872319887677</v>
+        <v>0.501634447701384</v>
       </c>
       <c r="S4">
-        <v>1341</v>
+        <v>448.5999999999999</v>
       </c>
       <c r="T4">
-        <v>0.4082937522835221</v>
+        <v>0.2491454023898187</v>
       </c>
       <c r="U4">
-        <v>16364.4</v>
+        <v>7690.1</v>
       </c>
       <c r="V4">
-        <v>0.4085717067763222</v>
+        <v>0.2253330871989616</v>
       </c>
       <c r="W4">
-        <v>0.2699961301634019</v>
+        <v>0.17051551348889</v>
       </c>
       <c r="X4">
-        <v>0.08811419881264031</v>
+        <v>0.08619221980511266</v>
       </c>
       <c r="Y4">
-        <v>0.1818819313507616</v>
+        <v>0.08432329368377733</v>
       </c>
       <c r="Z4">
-        <v>0.3408040374452525</v>
+        <v>2.689071129707112</v>
       </c>
       <c r="AA4">
-        <v>0.2653228715341729</v>
+        <v>0.3418624487447697</v>
       </c>
       <c r="AB4">
-        <v>0.07057519833586945</v>
+        <v>0.07626203481578087</v>
       </c>
       <c r="AC4">
-        <v>0.1947476731983034</v>
+        <v>0.2656004139289889</v>
       </c>
       <c r="AD4">
-        <v>20553.7</v>
+        <v>9174.299999999999</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>20553.7</v>
+        <v>9174.299999999999</v>
       </c>
       <c r="AG4">
-        <v>4189.300000000001</v>
+        <v>1484.199999999999</v>
       </c>
       <c r="AH4">
-        <v>0.3391341508487553</v>
+        <v>0.2118678121102951</v>
       </c>
       <c r="AI4">
-        <v>0.361847537326965</v>
+        <v>0.3234179513302569</v>
       </c>
       <c r="AJ4">
-        <v>0.09469056552597083</v>
+        <v>0.04167707985252118</v>
       </c>
       <c r="AK4">
-        <v>0.103598869371898</v>
+        <v>0.07178162754031123</v>
       </c>
       <c r="AL4">
-        <v>1330.6</v>
+        <v>441.9</v>
       </c>
       <c r="AM4">
-        <v>1330.6</v>
+        <v>441.9</v>
       </c>
       <c r="AN4">
-        <v>1.473668738752304</v>
+        <v>2.348710990502035</v>
       </c>
       <c r="AO4">
-        <v>10.40958965880054</v>
+        <v>8.010183299389002</v>
       </c>
       <c r="AP4">
-        <v>0.3003663791558224</v>
+        <v>0.379969790839968</v>
       </c>
       <c r="AQ4">
-        <v>10.40958965880054</v>
+        <v>8.010183299389002</v>
       </c>
     </row>
     <row r="5">
@@ -981,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Power Corporation of Canada (TSX:POW)</t>
+          <t>E-L Financial Corporation Limited (TSX:ELF)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,121 +990,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.00224</v>
+        <v>0.108</v>
       </c>
       <c r="E5">
-        <v>0.0457</v>
+        <v>0.5379999999999999</v>
       </c>
       <c r="G5">
-        <v>0.1133444882049397</v>
+        <v>0.3870369734628721</v>
       </c>
       <c r="H5">
-        <v>0.1133444882049397</v>
+        <v>0.3870369734628721</v>
       </c>
       <c r="I5">
-        <v>0.08276680461584622</v>
+        <v>0.6613683957568059</v>
       </c>
       <c r="J5">
-        <v>0.07669559212037975</v>
+        <v>0.5583766761122346</v>
       </c>
       <c r="K5">
-        <v>1218.3</v>
+        <v>1338.5</v>
       </c>
       <c r="L5">
-        <v>0.03293210035059455</v>
+        <v>0.4595077070960211</v>
       </c>
       <c r="M5">
-        <v>1278.9</v>
+        <v>107.907</v>
       </c>
       <c r="N5">
-        <v>0.06809287764153404</v>
+        <v>0.03478178184631253</v>
       </c>
       <c r="O5">
-        <v>1.049741442994337</v>
+        <v>0.08061785580874113</v>
       </c>
       <c r="P5">
-        <v>1004.6</v>
+        <v>37.407</v>
       </c>
       <c r="Q5">
-        <v>0.05348823588919001</v>
+        <v>0.01205743940175348</v>
       </c>
       <c r="R5">
-        <v>0.8245916440942297</v>
+        <v>0.02794695554725439</v>
       </c>
       <c r="S5">
-        <v>274.3000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="T5">
-        <v>0.2144811947767613</v>
+        <v>0.6533403764352638</v>
       </c>
       <c r="U5">
-        <v>7030.9</v>
+        <v>243.8</v>
       </c>
       <c r="V5">
-        <v>0.3743484349127075</v>
+        <v>0.07858432181536874</v>
       </c>
       <c r="W5">
-        <v>0.07495708563799351</v>
+        <v>0.2815464546391536</v>
       </c>
       <c r="X5">
-        <v>0.09593416297785629</v>
+        <v>0.0830695174133249</v>
       </c>
       <c r="Y5">
-        <v>-0.02097707733986277</v>
+        <v>0.1984769372258287</v>
       </c>
       <c r="Z5">
-        <v>2.932448178827633</v>
+        <v>0.5683374631728875</v>
       </c>
       <c r="AA5">
-        <v>0.2249058494375146</v>
+        <v>0.3173463835965364</v>
       </c>
       <c r="AB5">
-        <v>0.06879445403685272</v>
+        <v>0.07767464023665928</v>
       </c>
       <c r="AC5">
-        <v>0.1561113954006619</v>
+        <v>0.2396717433598772</v>
       </c>
       <c r="AD5">
-        <v>15218.6</v>
+        <v>443.2</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>15218.6</v>
+        <v>443.2</v>
       </c>
       <c r="AG5">
-        <v>8187.700000000001</v>
+        <v>199.4</v>
       </c>
       <c r="AH5">
-        <v>0.4476019329241212</v>
+        <v>0.125</v>
       </c>
       <c r="AI5">
-        <v>0.332842698767144</v>
+        <v>0.05968139400223536</v>
       </c>
       <c r="AJ5">
-        <v>0.3035922193300555</v>
+        <v>0.06039130171421648</v>
       </c>
       <c r="AK5">
-        <v>0.2116111257566125</v>
+        <v>0.02776269440151484</v>
       </c>
       <c r="AL5">
-        <v>913</v>
+        <v>158</v>
       </c>
       <c r="AM5">
-        <v>913</v>
+        <v>158</v>
       </c>
       <c r="AN5">
-        <v>4.202291868010493</v>
+        <v>0.2288783309233629</v>
       </c>
       <c r="AO5">
-        <v>3.353669222343921</v>
+        <v>12.19303797468354</v>
       </c>
       <c r="AP5">
-        <v>2.260858760182245</v>
+        <v>0.1029745920264408</v>
       </c>
       <c r="AQ5">
-        <v>3.353669222343921</v>
+        <v>12.19303797468354</v>
       </c>
     </row>
     <row r="6">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sun Life Financial Inc. (TSX:SLF)</t>
+          <t>Power Corporation of Canada (TSX:POW)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1124,121 +1124,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.007860000000000001</v>
+        <v>-0.06849999999999999</v>
       </c>
       <c r="E6">
-        <v>0.109</v>
+        <v>0.134</v>
       </c>
       <c r="G6">
-        <v>0.1837959143938967</v>
+        <v>0.1439006461098</v>
       </c>
       <c r="H6">
-        <v>0.1837959143938967</v>
+        <v>0.1439006461098</v>
       </c>
       <c r="I6">
-        <v>0.1900621499900089</v>
+        <v>0.1520988896196851</v>
       </c>
       <c r="J6">
-        <v>0.1661485807141575</v>
+        <v>0.1322166818262622</v>
       </c>
       <c r="K6">
-        <v>2786.9</v>
+        <v>1678.8</v>
       </c>
       <c r="L6">
-        <v>0.1427912672347097</v>
+        <v>0.06495144504197779</v>
       </c>
       <c r="M6">
-        <v>1405.431</v>
+        <v>1459</v>
       </c>
       <c r="N6">
-        <v>0.04622292019535939</v>
+        <v>0.0725376236097784</v>
       </c>
       <c r="O6">
-        <v>0.5042990419462484</v>
+        <v>0.8690731474862997</v>
       </c>
       <c r="P6">
-        <v>1267.931</v>
+        <v>1050.4</v>
       </c>
       <c r="Q6">
-        <v>0.04170071204222919</v>
+        <v>0.05222311161049435</v>
       </c>
       <c r="R6">
-        <v>0.4549610678531701</v>
+        <v>0.6256850131045986</v>
       </c>
       <c r="S6">
-        <v>137.5</v>
+        <v>408.5999999999999</v>
       </c>
       <c r="T6">
-        <v>0.09783475674010322</v>
+        <v>0.2800548320767648</v>
       </c>
       <c r="U6">
-        <v>6605.8</v>
+        <v>8311.200000000001</v>
       </c>
       <c r="V6">
-        <v>0.2172567463123448</v>
+        <v>0.4132108960559221</v>
       </c>
       <c r="W6">
-        <v>0.1444858049397565</v>
+        <v>0.1063797429853243</v>
       </c>
       <c r="X6">
-        <v>0.07868869536477927</v>
+        <v>0.09829090771309229</v>
       </c>
       <c r="Y6">
-        <v>0.06579710957497725</v>
+        <v>0.008088835272232017</v>
       </c>
       <c r="Z6">
-        <v>1.282792299552406</v>
+        <v>1.878101770779594</v>
       </c>
       <c r="AA6">
-        <v>0.2131341199216827</v>
+        <v>0.2483163842645052</v>
       </c>
       <c r="AB6">
-        <v>0.07286471346745965</v>
+        <v>0.07288702176943847</v>
       </c>
       <c r="AC6">
-        <v>0.140269406454223</v>
+        <v>0.1754293624950667</v>
       </c>
       <c r="AD6">
-        <v>4714.1</v>
+        <v>15223.4</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>4714.1</v>
+        <v>15223.4</v>
       </c>
       <c r="AG6">
-        <v>-1891.7</v>
+        <v>6912.199999999999</v>
       </c>
       <c r="AH6">
-        <v>0.1342298887231062</v>
+        <v>0.430805017955633</v>
       </c>
       <c r="AI6">
-        <v>0.2115511477101892</v>
+        <v>0.3260617665516495</v>
       </c>
       <c r="AJ6">
-        <v>-0.06634331446527646</v>
+        <v>0.2557620652781221</v>
       </c>
       <c r="AK6">
-        <v>-0.1206618317737933</v>
+        <v>0.1801107419712071</v>
       </c>
       <c r="AL6">
-        <v>416.9</v>
+        <v>564.8</v>
       </c>
       <c r="AM6">
-        <v>416.9</v>
+        <v>564.8</v>
       </c>
       <c r="AN6">
-        <v>1.164751809848541</v>
+        <v>3.405529953917051</v>
       </c>
       <c r="AO6">
-        <v>8.897817222355481</v>
+        <v>6.96051699716714</v>
       </c>
       <c r="AP6">
-        <v>-0.467398018432041</v>
+        <v>1.546284282582435</v>
       </c>
       <c r="AQ6">
-        <v>8.897817222355481</v>
+        <v>6.96051699716714</v>
       </c>
     </row>
     <row r="7">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Great-West Lifeco Inc. (TSX:GWO)</t>
+          <t>iA Financial Corporation Inc. (TSX:IAG)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1258,121 +1258,121 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0008699999999999999</v>
+        <v>-0.0999</v>
       </c>
       <c r="E7">
-        <v>-0.0452</v>
+        <v>0.0759</v>
       </c>
       <c r="G7">
-        <v>0.1062784966845633</v>
+        <v>0.1411606542684293</v>
       </c>
       <c r="H7">
-        <v>0.1062784966845633</v>
+        <v>0.1411606542684293</v>
       </c>
       <c r="I7">
-        <v>0.07731157962405208</v>
+        <v>0.1503771752931511</v>
       </c>
       <c r="J7">
-        <v>0.07706355474316068</v>
+        <v>0.1153713925585214</v>
       </c>
       <c r="K7">
-        <v>1628.5</v>
+        <v>734.3</v>
       </c>
       <c r="L7">
-        <v>0.04846668492041761</v>
+        <v>0.1096870565389499</v>
       </c>
       <c r="M7">
-        <v>1537.6</v>
+        <v>747.6</v>
       </c>
       <c r="N7">
-        <v>0.04964516108201655</v>
+        <v>0.08626817447495962</v>
       </c>
       <c r="O7">
-        <v>0.9441817623579982</v>
+        <v>1.018112488083889</v>
       </c>
       <c r="P7">
-        <v>1411.2</v>
+        <v>232.4</v>
       </c>
       <c r="Q7">
-        <v>0.04556402921367179</v>
+        <v>0.02681744749596123</v>
       </c>
       <c r="R7">
-        <v>0.8665643229966227</v>
+        <v>0.3164918970448046</v>
       </c>
       <c r="S7">
-        <v>126.4000000000001</v>
+        <v>515.2</v>
       </c>
       <c r="T7">
-        <v>0.08220603537981275</v>
+        <v>0.6891385767790262</v>
       </c>
       <c r="U7">
-        <v>5158.4</v>
+        <v>1552.2</v>
       </c>
       <c r="V7">
-        <v>0.16655150814612</v>
+        <v>0.1791137779829218</v>
       </c>
       <c r="W7">
-        <v>0.08813326333905193</v>
+        <v>0.1498449106195413</v>
       </c>
       <c r="X7">
-        <v>0.08039181098578307</v>
+        <v>0.08646707559163003</v>
       </c>
       <c r="Y7">
-        <v>0.007741452353268855</v>
+        <v>0.06337783502791125</v>
       </c>
       <c r="Z7">
-        <v>2.431200028942514</v>
+        <v>1.221133851373536</v>
       </c>
       <c r="AA7">
-        <v>0.1873569165219852</v>
+        <v>0.1408839129333154</v>
       </c>
       <c r="AB7">
-        <v>0.07226813478323242</v>
+        <v>0.07628538248664009</v>
       </c>
       <c r="AC7">
-        <v>0.1150887817387528</v>
+        <v>0.06459853044667531</v>
       </c>
       <c r="AD7">
-        <v>6806.1</v>
+        <v>2425.7</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>6806.1</v>
+        <v>2425.7</v>
       </c>
       <c r="AG7">
-        <v>1647.700000000001</v>
+        <v>873.4999999999998</v>
       </c>
       <c r="AH7">
-        <v>0.180160887714775</v>
+        <v>0.2186950602702922</v>
       </c>
       <c r="AI7">
-        <v>0.2376846516500786</v>
+        <v>0.3090614886731392</v>
       </c>
       <c r="AJ7">
-        <v>0.05051273011542178</v>
+        <v>0.09156664395408562</v>
       </c>
       <c r="AK7">
-        <v>0.07018477973812225</v>
+        <v>0.138730067975351</v>
       </c>
       <c r="AL7">
-        <v>640.9</v>
+        <v>43.7</v>
       </c>
       <c r="AM7">
-        <v>640.9</v>
+        <v>43.7</v>
       </c>
       <c r="AN7">
-        <v>2.287457148618673</v>
+        <v>2.097993426742778</v>
       </c>
       <c r="AO7">
-        <v>4.053206428459978</v>
+        <v>23.03661327231121</v>
       </c>
       <c r="AP7">
-        <v>0.5537742824494188</v>
+        <v>0.7554921293893788</v>
       </c>
       <c r="AQ7">
-        <v>4.053206428459978</v>
+        <v>23.03661327231121</v>
       </c>
     </row>
     <row r="8">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>E-L Financial Corporation Limited (TSX:ELF)</t>
+          <t>Manulife Financial Corporation (TSX:MFC)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1392,121 +1392,115 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.105</v>
+        <v>-0.167</v>
       </c>
       <c r="E8">
-        <v>0.131</v>
+        <v>0.0483</v>
       </c>
       <c r="G8">
-        <v>-0.2736965436438196</v>
+        <v>0.2843990550869913</v>
       </c>
       <c r="H8">
-        <v>-0.2736965436438196</v>
+        <v>0.2843990550869913</v>
       </c>
       <c r="I8">
-        <v>1.202108963093146</v>
+        <v>0.2954335192620338</v>
       </c>
       <c r="J8">
-        <v>1.020393371258786</v>
+        <v>0.2484955885626278</v>
       </c>
       <c r="K8">
-        <v>716.8</v>
+        <v>4225.2</v>
       </c>
       <c r="L8">
-        <v>0.8398359695371997</v>
+        <v>0.1897550591468837</v>
       </c>
       <c r="M8">
-        <v>38.422</v>
+        <v>3689.2</v>
       </c>
       <c r="N8">
-        <v>0.01399198834668609</v>
+        <v>0.06861381203550093</v>
       </c>
       <c r="O8">
-        <v>0.05360212053571428</v>
+        <v>0.8731420997822589</v>
       </c>
       <c r="P8">
-        <v>35.29199999999999</v>
+        <v>2080</v>
       </c>
       <c r="Q8">
-        <v>0.01285214857975236</v>
+        <v>0.03868500732783312</v>
       </c>
       <c r="R8">
-        <v>0.04923549107142856</v>
+        <v>0.4922843889046672</v>
       </c>
       <c r="S8">
-        <v>3.130000000000003</v>
+        <v>1609.2</v>
       </c>
       <c r="T8">
-        <v>0.08146374472958208</v>
+        <v>0.4361921283747154</v>
       </c>
       <c r="U8">
-        <v>274.5</v>
+        <v>16939.2</v>
       </c>
       <c r="V8">
-        <v>0.09996358339402768</v>
+        <v>0.315044748138284</v>
       </c>
       <c r="W8">
-        <v>0.165032002578625</v>
+        <v>0.126805580982164</v>
       </c>
       <c r="X8">
-        <v>0.07884451360161396</v>
+        <v>0.08701657310899452</v>
       </c>
       <c r="Y8">
-        <v>0.08618748897701109</v>
+        <v>0.0397890078731695</v>
       </c>
       <c r="Z8">
-        <v>0.1791524107386495</v>
+        <v>0.565761022844787</v>
       </c>
       <c r="AA8">
-        <v>0.1828059323627494</v>
+        <v>0.1405891183576096</v>
       </c>
       <c r="AB8">
-        <v>0.07295940926914427</v>
+        <v>0.07608816869489389</v>
       </c>
       <c r="AC8">
-        <v>0.1098465230936051</v>
+        <v>0.06450094966271573</v>
       </c>
       <c r="AD8">
-        <v>442</v>
+        <v>16241.9</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>442</v>
+        <v>16241.9</v>
       </c>
       <c r="AG8">
-        <v>167.5</v>
+        <v>-697.3000000000011</v>
       </c>
       <c r="AH8">
-        <v>0.1386449184441656</v>
+        <v>0.2319956577321649</v>
       </c>
       <c r="AI8">
-        <v>0.07094133697135062</v>
+        <v>0.2982020008776101</v>
       </c>
       <c r="AJ8">
-        <v>0.05749099021795092</v>
+        <v>-0.01313917577251308</v>
       </c>
       <c r="AK8">
-        <v>0.02812290127602418</v>
+        <v>-0.01858133765378971</v>
       </c>
       <c r="AL8">
-        <v>59.5</v>
+        <v>1222.1</v>
       </c>
       <c r="AM8">
-        <v>59.5</v>
-      </c>
-      <c r="AN8">
-        <v>0.4282530762523012</v>
+        <v>1222.1</v>
       </c>
       <c r="AO8">
-        <v>17.2436974789916</v>
-      </c>
-      <c r="AP8">
-        <v>0.162290475729096</v>
+        <v>5.382783732918747</v>
       </c>
       <c r="AQ8">
-        <v>17.2436974789916</v>
+        <v>5.382783732918747</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/canada/canada_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_insurance_life.xlsx
@@ -645,10 +645,10 @@
         <v>0.1523486789691678</v>
       </c>
       <c r="X2">
-        <v>0.08632964769837134</v>
+        <v>0.08630359073841379</v>
       </c>
       <c r="Y2">
-        <v>0.06601903127079642</v>
+        <v>0.06604508823075397</v>
       </c>
       <c r="Z2">
         <v>1.237234941221992</v>
@@ -657,10 +657,10 @@
         <v>0.2828313839305208</v>
       </c>
       <c r="AB2">
-        <v>0.07627370865121047</v>
+        <v>0.0762532615726224</v>
       </c>
       <c r="AC2">
-        <v>0.2075505529274719</v>
+        <v>0.2075706401666007</v>
       </c>
       <c r="AD2">
         <v>50253.4</v>
@@ -779,10 +779,10 @@
         <v>0.1548524473187942</v>
       </c>
       <c r="X3">
-        <v>0.08494432910377495</v>
+        <v>0.08491916278050432</v>
       </c>
       <c r="Y3">
-        <v>0.06990811821501927</v>
+        <v>0.0699332845382899</v>
       </c>
       <c r="Z3">
         <v>1.843866615813759</v>
@@ -791,10 +791,10 @@
         <v>0.4200384672772585</v>
       </c>
       <c r="AB3">
-        <v>0.07676395269355669</v>
+        <v>0.07674329890302005</v>
       </c>
       <c r="AC3">
-        <v>0.3432745145837018</v>
+        <v>0.3432951683742385</v>
       </c>
       <c r="AD3">
         <v>6744.9</v>
@@ -913,10 +913,10 @@
         <v>0.17051551348889</v>
       </c>
       <c r="X4">
-        <v>0.08619221980511266</v>
+        <v>0.08616625119907168</v>
       </c>
       <c r="Y4">
-        <v>0.08432329368377733</v>
+        <v>0.08434926228981832</v>
       </c>
       <c r="Z4">
         <v>2.689071129707112</v>
@@ -925,10 +925,10 @@
         <v>0.3418624487447697</v>
       </c>
       <c r="AB4">
-        <v>0.07626203481578087</v>
+        <v>0.07624156812148535</v>
       </c>
       <c r="AC4">
-        <v>0.2656004139289889</v>
+        <v>0.2656208806232844</v>
       </c>
       <c r="AD4">
         <v>9174.299999999999</v>
@@ -1047,10 +1047,10 @@
         <v>0.2815464546391536</v>
       </c>
       <c r="X5">
-        <v>0.0830695174133249</v>
+        <v>0.08304555642728072</v>
       </c>
       <c r="Y5">
-        <v>0.1984769372258287</v>
+        <v>0.1985008982118728</v>
       </c>
       <c r="Z5">
         <v>0.5683374631728875</v>
@@ -1059,10 +1059,10 @@
         <v>0.3173463835965364</v>
       </c>
       <c r="AB5">
-        <v>0.07767464023665928</v>
+        <v>0.07765367437387062</v>
       </c>
       <c r="AC5">
-        <v>0.2396717433598772</v>
+        <v>0.2396927092226658</v>
       </c>
       <c r="AD5">
         <v>443.2</v>
@@ -1181,10 +1181,10 @@
         <v>0.1063797429853243</v>
       </c>
       <c r="X6">
-        <v>0.09829090771309229</v>
+        <v>0.09825716072642725</v>
       </c>
       <c r="Y6">
-        <v>0.008088835272232017</v>
+        <v>0.00812258225889706</v>
       </c>
       <c r="Z6">
         <v>1.878101770779594</v>
@@ -1193,10 +1193,10 @@
         <v>0.2483163842645052</v>
       </c>
       <c r="AB6">
-        <v>0.07288702176943847</v>
+        <v>0.0728678131539696</v>
       </c>
       <c r="AC6">
-        <v>0.1754293624950667</v>
+        <v>0.1754485711105356</v>
       </c>
       <c r="AD6">
         <v>15223.4</v>
@@ -1315,10 +1315,10 @@
         <v>0.1498449106195413</v>
       </c>
       <c r="X7">
-        <v>0.08646707559163003</v>
+        <v>0.0864409302777559</v>
       </c>
       <c r="Y7">
-        <v>0.06337783502791125</v>
+        <v>0.06340398034178538</v>
       </c>
       <c r="Z7">
         <v>1.221133851373536</v>
@@ -1327,10 +1327,10 @@
         <v>0.1408839129333154</v>
       </c>
       <c r="AB7">
-        <v>0.07628538248664009</v>
+        <v>0.07626495502375945</v>
       </c>
       <c r="AC7">
-        <v>0.06459853044667531</v>
+        <v>0.06461895790955595</v>
       </c>
       <c r="AD7">
         <v>2425.7</v>
@@ -1449,10 +1449,10 @@
         <v>0.126805580982164</v>
       </c>
       <c r="X8">
-        <v>0.08701657310899452</v>
+        <v>0.08699007451707284</v>
       </c>
       <c r="Y8">
-        <v>0.0397890078731695</v>
+        <v>0.03981550646509117</v>
       </c>
       <c r="Z8">
         <v>0.565761022844787</v>
@@ -1461,10 +1461,10 @@
         <v>0.1405891183576096</v>
       </c>
       <c r="AB8">
-        <v>0.07608816869489389</v>
+        <v>0.07606781766123406</v>
       </c>
       <c r="AC8">
-        <v>0.06450094966271573</v>
+        <v>0.06452130069637556</v>
       </c>
       <c r="AD8">
         <v>16241.9</v>
